--- a/lottopy_site/lottopy/lottopy_web_edition/lotto_megamil.xlsx
+++ b/lottopy_site/lottopy/lottopy_web_edition/lotto_megamil.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,16 +456,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05/20/2022</t>
+          <t>05/27/2022</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>33–40–59–60–69</t>
+          <t>3–14–40–53–54</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -477,19 +477,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05/17/2022</t>
+          <t>05/24/2022</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7–21–24–41–65</t>
+          <t>3–5–6–63–68</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -498,16 +498,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05/13/2022</t>
+          <t>05/20/2022</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11–41–43–44–65</t>
+          <t>33–40–59–60–69</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -519,19 +519,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05/10/2022</t>
+          <t>05/17/2022</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15–19–20–61–70</t>
+          <t>7–21–24–41–65</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -540,19 +540,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05/06/2022</t>
+          <t>05/13/2022</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16–21–33–52–70</t>
+          <t>11–41–43–44–65</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -561,19 +561,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05/03/2022</t>
+          <t>05/10/2022</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15–19–27–35–57</t>
+          <t>15–19–20–61–70</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -582,16 +582,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>04/29/2022</t>
+          <t>05/06/2022</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9–11–34–49–66</t>
+          <t>16–21–33–52–70</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -603,19 +603,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>04/26/2022</t>
+          <t>05/03/2022</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5–7–19–46–69</t>
+          <t>15–19–27–35–57</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -624,19 +624,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>04/22/2022</t>
+          <t>04/29/2022</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7–28–29–58–59</t>
+          <t>9–11–34–49–66</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -645,19 +645,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>04/19/2022</t>
+          <t>04/26/2022</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2–9–33–47–53</t>
+          <t>5–7–19–46–69</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -666,19 +666,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>04/15/2022</t>
+          <t>04/22/2022</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4–17–20–46–64</t>
+          <t>7–28–29–58–59</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -687,19 +687,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>04/12/2022</t>
+          <t>04/19/2022</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2–8–14–20–31</t>
+          <t>2–9–33–47–53</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -708,19 +708,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>04/08/2022</t>
+          <t>04/15/2022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8–11–29–32–40</t>
+          <t>4–17–20–46–64</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -729,16 +729,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>04/05/2022</t>
+          <t>04/12/2022</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>22–43–60–63–64</t>
+          <t>2–8–14–20–31</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -750,19 +750,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>04/01/2022</t>
+          <t>04/08/2022</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>26–42–47–48–63</t>
+          <t>8–11–29–32–40</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -771,16 +771,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>03/29/2022</t>
+          <t>04/05/2022</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7–22–36–45–47</t>
+          <t>22–43–60–63–64</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -792,19 +792,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>03/25/2022</t>
+          <t>04/01/2022</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3–13–42–51–58</t>
+          <t>26–42–47–48–63</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -813,19 +813,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>03/22/2022</t>
+          <t>03/29/2022</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>8–15–21–27–61</t>
+          <t>7–22–36–45–47</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -834,19 +834,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>03/18/2022</t>
+          <t>03/25/2022</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2–6–25–40–45</t>
+          <t>3–13–42–51–58</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -855,19 +855,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>03/15/2022</t>
+          <t>03/22/2022</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9–14–28–59–60</t>
+          <t>8–15–21–27–61</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -876,19 +876,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>03/11/2022</t>
+          <t>03/18/2022</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>24–28–39–44–66</t>
+          <t>2–6–25–40–45</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -897,19 +897,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>03/08/2022</t>
+          <t>03/15/2022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>7–18–38–58–64</t>
+          <t>9–14–28–59–60</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -918,19 +918,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>03/04/2022</t>
+          <t>03/11/2022</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11–19–28–46–47</t>
+          <t>24–28–39–44–66</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -939,19 +939,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>03/01/2022</t>
+          <t>03/08/2022</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18–22–38–39–50</t>
+          <t>7–18–38–58–64</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -960,19 +960,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>02/25/2022</t>
+          <t>03/04/2022</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15–31–40–56–66</t>
+          <t>11–19–28–46–47</t>
         </is>
       </c>
       <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
         <v>4</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -981,19 +981,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>02/22/2022</t>
+          <t>03/01/2022</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>6–17–22–57–62</t>
+          <t>18–22–38–39–50</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1002,19 +1002,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>02/18/2022</t>
+          <t>02/25/2022</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>6–11–50–63–68</t>
+          <t>15–31–40–56–66</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1023,16 +1023,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>02/15/2022</t>
+          <t>02/22/2022</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2–4–15–21–63</t>
+          <t>6–17–22–57–62</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
         <v>3</v>
@@ -1044,19 +1044,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>02/11/2022</t>
+          <t>02/18/2022</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>11–16–23–24–30</t>
+          <t>6–11–50–63–68</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1065,16 +1065,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>02/08/2022</t>
+          <t>02/15/2022</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1–17–20–52–54</t>
+          <t>2–4–15–21–63</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
@@ -1086,19 +1086,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>02/04/2022</t>
+          <t>02/11/2022</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>7–16–34–44–61</t>
+          <t>11–16–23–24–30</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>24</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -1107,19 +1107,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>02/01/2022</t>
+          <t>02/08/2022</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>11–24–38–62–66</t>
+          <t>1–17–20–52–54</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1128,19 +1128,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01/28/2022</t>
+          <t>02/04/2022</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3–16–25–44–55</t>
+          <t>7–16–34–44–61</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -1149,19 +1149,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01/25/2022</t>
+          <t>02/01/2022</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3–12–38–53–58</t>
+          <t>11–24–38–62–66</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -1170,19 +1170,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01/21/2022</t>
+          <t>01/28/2022</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>38–45–46–55–67</t>
+          <t>3–16–25–44–55</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1191,19 +1191,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01/18/2022</t>
+          <t>01/25/2022</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>4–19–39–42–52</t>
+          <t>3–12–38–53–58</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1212,16 +1212,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01/14/2022</t>
+          <t>01/21/2022</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5–8–13–22–48</t>
+          <t>38–45–46–55–67</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E38" t="n">
         <v>2</v>
@@ -1233,19 +1233,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01/11/2022</t>
+          <t>01/18/2022</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2–3–19–52–58</t>
+          <t>4–19–39–42–52</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -1254,19 +1254,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01/07/2022</t>
+          <t>01/14/2022</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>7–29–43–56–57</t>
+          <t>5–8–13–22–48</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -1275,19 +1275,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
+          <t>01/11/2022</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>4–6–16–21–22</t>
+          <t>2–3–19–52–58</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1296,16 +1296,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12/31/2021</t>
+          <t>01/07/2022</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2–5–30–46–61</t>
+          <t>7–29–43–56–57</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
         <v>3</v>
@@ -1317,16 +1317,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12/28/2021</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3–5–8–31–38</t>
+          <t>4–6–16–21–22</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>3</v>
@@ -1338,19 +1338,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12/24/2021</t>
+          <t>12/31/2021</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>16–17–25–36–37</t>
+          <t>2–5–30–46–61</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -1359,16 +1359,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12/21/2021</t>
+          <t>12/28/2021</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>25–31–58–64–67</t>
+          <t>3–5–8–31–38</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
         <v>3</v>
@@ -1380,19 +1380,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12/17/2021</t>
+          <t>12/24/2021</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>21–32–38–48–62</t>
+          <t>16–17–25–36–37</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1401,16 +1401,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12/14/2021</t>
+          <t>12/21/2021</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>33–35–44–55–69</t>
+          <t>25–31–58–64–67</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E47" t="n">
         <v>3</v>
@@ -1422,19 +1422,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12/10/2021</t>
+          <t>12/17/2021</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>23–25–40–42–60</t>
+          <t>21–32–38–48–62</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -1443,19 +1443,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12/07/2021</t>
+          <t>12/14/2021</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1–7–40–43–68</t>
+          <t>33–35–44–55–69</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -1464,19 +1464,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12/03/2021</t>
+          <t>12/10/2021</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>22–45–48–58–61</t>
+          <t>23–25–40–42–60</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11/30/2021</t>
+          <t>12/07/2021</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>7–8–26–30–39</t>
+          <t>1–7–40–43–68</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
         <v>2</v>
@@ -1506,19 +1506,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11/26/2021</t>
+          <t>12/03/2021</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>7–27–37–42–59</t>
+          <t>22–45–48–58–61</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -1527,19 +1527,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11/23/2021</t>
+          <t>11/30/2021</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>7–24–54–57–58</t>
+          <t>7–8–26–30–39</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -1548,19 +1548,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>11/19/2021</t>
+          <t>11/26/2021</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>5–23–52–53–59</t>
+          <t>7–27–37–42–59</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -1569,16 +1569,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11/16/2021</t>
+          <t>11/23/2021</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>6–22–44–53–65</t>
+          <t>7–24–54–57–58</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E55" t="n">
         <v>3</v>
@@ -1590,19 +1590,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11/12/2021</t>
+          <t>11/19/2021</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>30–32–42–46–48</t>
+          <t>5–23–52–53–59</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -1611,16 +1611,16 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11/09/2021</t>
+          <t>11/16/2021</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9–14–16–26–49</t>
+          <t>6–22–44–53–65</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
         <v>3</v>
@@ -1632,16 +1632,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11/05/2021</t>
+          <t>11/12/2021</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>10–15–20–66–68</t>
+          <t>30–32–42–46–48</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E58" t="n">
         <v>2</v>
@@ -1653,19 +1653,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11/02/2021</t>
+          <t>11/09/2021</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>5–10–26–58–65</t>
+          <t>9–14–16–26–49</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -1674,19 +1674,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10/29/2021</t>
+          <t>11/05/2021</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>15–26–28–35–45</t>
+          <t>10–15–20–66–68</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -1695,19 +1695,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>10/26/2021</t>
+          <t>11/02/2021</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>6–14–19–56–62</t>
+          <t>5–10–26–58–65</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>9</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -1716,16 +1716,16 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>10/22/2021</t>
+          <t>10/29/2021</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9–14–26–29–66</t>
+          <t>15–26–28–35–45</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
         <v>3</v>
@@ -1737,19 +1737,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>10/19/2021</t>
+          <t>10/26/2021</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>3–12–13–19–52</t>
+          <t>6–14–19–56–62</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -1758,16 +1758,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>10/15/2021</t>
+          <t>10/22/2021</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>3–20–31–34–65</t>
+          <t>9–14–26–29–66</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E64" t="n">
         <v>3</v>
@@ -1779,16 +1779,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>10/12/2021</t>
+          <t>10/19/2021</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>21–26–56–61–65</t>
+          <t>3–12–13–19–52</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
         <v>3</v>
@@ -1800,19 +1800,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10/08/2021</t>
+          <t>10/15/2021</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>21–24–36–40–70</t>
+          <t>3–20–31–34–65</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>10/05/2021</t>
+          <t>10/12/2021</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>7–11–18–30–36</t>
+          <t>21–26–56–61–65</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -1842,19 +1842,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>10/01/2021</t>
+          <t>10/08/2021</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>21–25–36–62–63</t>
+          <t>21–24–36–40–70</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -1863,19 +1863,19 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>09/28/2021</t>
+          <t>10/05/2021</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>18–30–43–68–69</t>
+          <t>7–11–18–30–36</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -1884,19 +1884,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>09/24/2021</t>
+          <t>10/01/2021</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>17–21–27–43–56</t>
+          <t>21–25–36–62–63</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -1905,19 +1905,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>09/21/2021</t>
+          <t>09/28/2021</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>36–41–45–51–56</t>
+          <t>18–30–43–68–69</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -1926,16 +1926,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>09/17/2021</t>
+          <t>09/24/2021</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>17–32–40–59–61</t>
+          <t>17–21–27–43–56</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E72" t="n">
         <v>3</v>
@@ -1947,19 +1947,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>09/14/2021</t>
+          <t>09/21/2021</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>4–13–19–63–64</t>
+          <t>36–41–45–51–56</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -1968,19 +1968,19 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>09/10/2021</t>
+          <t>09/17/2021</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>20–32–35–47–64</t>
+          <t>17–32–40–59–61</t>
         </is>
       </c>
       <c r="D74" t="n">
         <v>18</v>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -1989,19 +1989,19 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>09/07/2021</t>
+          <t>09/14/2021</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>15–17–25–32–53</t>
+          <t>4–13–19–63–64</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -2010,16 +2010,16 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>09/03/2021</t>
+          <t>09/10/2021</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>7–10–12–61–65</t>
+          <t>20–32–35–47–64</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E76" t="n">
         <v>2</v>
@@ -2031,16 +2031,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>08/31/2021</t>
+          <t>09/07/2021</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>8–14–31–58–68</t>
+          <t>15–17–25–32–53</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E77" t="n">
         <v>3</v>
@@ -2052,19 +2052,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>08/27/2021</t>
+          <t>09/03/2021</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1–10–44–47–56</t>
+          <t>7–10–12–61–65</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2073,19 +2073,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>08/24/2021</t>
+          <t>08/31/2021</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>17–18–26–52–67</t>
+          <t>8–14–31–58–68</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2094,19 +2094,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>08/20/2021</t>
+          <t>08/27/2021</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>41–43–51–57–70</t>
+          <t>1–10–44–47–56</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2115,19 +2115,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>08/17/2021</t>
+          <t>08/24/2021</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>3–6–16–38–56</t>
+          <t>17–18–26–52–67</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -2136,16 +2136,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>08/13/2021</t>
+          <t>08/20/2021</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>17–21–35–40–53</t>
+          <t>41–43–51–57–70</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
         <v>2</v>
@@ -2157,19 +2157,19 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>08/10/2021</t>
+          <t>08/17/2021</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>29–45–50–59–62</t>
+          <t>3–6–16–38–56</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2178,16 +2178,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>08/06/2021</t>
+          <t>08/13/2021</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9–18–40–46–69</t>
+          <t>17–21–35–40–53</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
@@ -2199,16 +2199,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>08/03/2021</t>
+          <t>08/10/2021</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1–9–17–27–34</t>
+          <t>29–45–50–59–62</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E85" t="n">
         <v>2</v>
@@ -2220,19 +2220,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>07/30/2021</t>
+          <t>08/06/2021</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>19–26–31–52–68</t>
+          <t>9–18–40–46–69</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2241,19 +2241,19 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>07/27/2021</t>
+          <t>08/03/2021</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2–35–36–54–64</t>
+          <t>1–9–17–27–34</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -2262,16 +2262,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>07/23/2021</t>
+          <t>07/30/2021</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>13–17–19–40–69</t>
+          <t>19–26–31–52–68</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E88" t="n">
         <v>3</v>
@@ -2283,19 +2283,19 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>07/20/2021</t>
+          <t>07/27/2021</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>10–26–30–52–57</t>
+          <t>2–35–36–54–64</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -2304,19 +2304,19 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>07/16/2021</t>
+          <t>07/23/2021</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>24–25–47–52–57</t>
+          <t>13–17–19–40–69</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -2325,16 +2325,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>07/13/2021</t>
+          <t>07/20/2021</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>3–10–17–26–55</t>
+          <t>10–26–30–52–57</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E91" t="n">
         <v>2</v>
@@ -2346,19 +2346,19 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>07/09/2021</t>
+          <t>07/16/2021</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>6–37–39–41–46</t>
+          <t>24–25–47–52–57</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
@@ -2367,19 +2367,19 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>07/06/2021</t>
+          <t>07/13/2021</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>18–47–63–68–69</t>
+          <t>3–10–17–26–55</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -2388,16 +2388,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>07/02/2021</t>
+          <t>07/09/2021</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>8–31–32–34–45</t>
+          <t>6–37–39–41–46</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E94" t="n">
         <v>2</v>
@@ -2409,16 +2409,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>06/29/2021</t>
+          <t>07/06/2021</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>7–38–50–52–69</t>
+          <t>18–47–63–68–69</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E95" t="n">
         <v>3</v>
@@ -2430,19 +2430,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>06/25/2021</t>
+          <t>07/02/2021</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>17–20–42–45–65</t>
+          <t>8–31–32–34–45</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E96" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -2451,19 +2451,19 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>06/22/2021</t>
+          <t>06/29/2021</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1–26–48–51–59</t>
+          <t>7–38–50–52–69</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
@@ -2472,19 +2472,19 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>06/18/2021</t>
+          <t>06/25/2021</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>14–36–44–46–53</t>
+          <t>17–20–42–45–65</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
@@ -2493,16 +2493,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>06/15/2021</t>
+          <t>06/22/2021</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>18–22–27–38–52</t>
+          <t>1–26–48–51–59</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E99" t="n">
         <v>4</v>
@@ -2514,19 +2514,19 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>06/11/2021</t>
+          <t>06/18/2021</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>4–43–56–63–68</t>
+          <t>14–36–44–46–53</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -2535,19 +2535,19 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>06/08/2021</t>
+          <t>06/15/2021</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>9–22–39–41–54</t>
+          <t>18–22–27–38–52</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
@@ -2556,19 +2556,19 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>06/04/2021</t>
+          <t>06/11/2021</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>4–30–34–41–64</t>
+          <t>4–43–56–63–68</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
@@ -2577,19 +2577,19 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>06/01/2021</t>
+          <t>06/08/2021</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7–11–33–58–63</t>
+          <t>9–22–39–41–54</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2598,19 +2598,19 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>05/28/2021</t>
+          <t>06/04/2021</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>10–14–20–47–70</t>
+          <t>4–30–34–41–64</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2619,19 +2619,40 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>05/25/2021</t>
+          <t>06/01/2021</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>14–21–31–34–54</t>
+          <t>7–11–33–58–63</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E105" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>05/28/2021</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>10–14–20–47–70</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>15</v>
+      </c>
+      <c r="E106" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/lottopy_site/lottopy/lottopy_web_edition/lotto_megamil.xlsx
+++ b/lottopy_site/lottopy/lottopy_web_edition/lotto_megamil.xlsx
@@ -456,19 +456,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05/27/2022</t>
+          <t>06/07/2022</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3–14–40–53–54</t>
+          <t>4–34–40–41–53</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05/24/2022</t>
+          <t>06/03/2022</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3–5–6–63–68</t>
+          <t>11–16–22–48–59</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -498,19 +498,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05/20/2022</t>
+          <t>05/31/2022</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33–40–59–60–69</t>
+          <t>6–15–41–63–64</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -519,19 +519,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05/17/2022</t>
+          <t>05/27/2022</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7–21–24–41–65</t>
+          <t>3–14–40–53–54</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -540,16 +540,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05/13/2022</t>
+          <t>05/24/2022</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11–41–43–44–65</t>
+          <t>3–5–6–63–68</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -561,16 +561,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05/10/2022</t>
+          <t>05/20/2022</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15–19–20–61–70</t>
+          <t>33–40–59–60–69</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -582,19 +582,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>05/06/2022</t>
+          <t>05/17/2022</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16–21–33–52–70</t>
+          <t>7–21–24–41–65</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -603,19 +603,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>05/03/2022</t>
+          <t>05/13/2022</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15–19–27–35–57</t>
+          <t>11–41–43–44–65</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -624,19 +624,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>04/29/2022</t>
+          <t>05/10/2022</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9–11–34–49–66</t>
+          <t>15–19–20–61–70</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -645,19 +645,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>04/26/2022</t>
+          <t>05/06/2022</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5–7–19–46–69</t>
+          <t>16–21–33–52–70</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -666,19 +666,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>04/22/2022</t>
+          <t>05/03/2022</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>7–28–29–58–59</t>
+          <t>15–19–27–35–57</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -687,19 +687,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>04/19/2022</t>
+          <t>04/29/2022</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2–9–33–47–53</t>
+          <t>9–11–34–49–66</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -708,16 +708,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>04/15/2022</t>
+          <t>04/26/2022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4–17–20–46–64</t>
+          <t>5–7–19–46–69</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
@@ -729,19 +729,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>04/12/2022</t>
+          <t>04/22/2022</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2–8–14–20–31</t>
+          <t>7–28–29–58–59</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -750,16 +750,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>04/08/2022</t>
+          <t>04/19/2022</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8–11–29–32–40</t>
+          <t>2–9–33–47–53</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
@@ -771,19 +771,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>04/05/2022</t>
+          <t>04/15/2022</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22–43–60–63–64</t>
+          <t>4–17–20–46–64</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -792,19 +792,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>04/01/2022</t>
+          <t>04/12/2022</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>26–42–47–48–63</t>
+          <t>2–8–14–20–31</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -813,19 +813,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>03/29/2022</t>
+          <t>04/08/2022</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7–22–36–45–47</t>
+          <t>8–11–29–32–40</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -834,16 +834,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>03/25/2022</t>
+          <t>04/05/2022</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3–13–42–51–58</t>
+          <t>22–43–60–63–64</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
@@ -855,19 +855,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>03/22/2022</t>
+          <t>04/01/2022</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8–15–21–27–61</t>
+          <t>26–42–47–48–63</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -876,19 +876,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>03/18/2022</t>
+          <t>03/29/2022</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2–6–25–40–45</t>
+          <t>7–22–36–45–47</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -897,19 +897,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>03/15/2022</t>
+          <t>03/25/2022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9–14–28–59–60</t>
+          <t>3–13–42–51–58</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -918,16 +918,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>03/11/2022</t>
+          <t>03/22/2022</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>24–28–39–44–66</t>
+          <t>8–15–21–27–61</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
         <v>3</v>
@@ -939,19 +939,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>03/08/2022</t>
+          <t>03/18/2022</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7–18–38–58–64</t>
+          <t>2–6–25–40–45</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -960,19 +960,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>03/04/2022</t>
+          <t>03/15/2022</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>11–19–28–46–47</t>
+          <t>9–14–28–59–60</t>
         </is>
       </c>
       <c r="D26" t="n">
+        <v>24</v>
+      </c>
+      <c r="E26" t="n">
         <v>5</v>
-      </c>
-      <c r="E26" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -981,19 +981,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>03/01/2022</t>
+          <t>03/11/2022</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18–22–38–39–50</t>
+          <t>24–28–39–44–66</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1002,16 +1002,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>02/25/2022</t>
+          <t>03/08/2022</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15–31–40–56–66</t>
+          <t>7–18–38–58–64</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E28" t="n">
         <v>3</v>
@@ -1023,19 +1023,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>02/22/2022</t>
+          <t>03/04/2022</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6–17–22–57–62</t>
+          <t>11–19–28–46–47</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1044,19 +1044,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>02/18/2022</t>
+          <t>03/01/2022</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6–11–50–63–68</t>
+          <t>18–22–38–39–50</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1065,16 +1065,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>02/15/2022</t>
+          <t>02/25/2022</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2–4–15–21–63</t>
+          <t>15–31–40–56–66</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>02/11/2022</t>
+          <t>02/22/2022</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>11–16–23–24–30</t>
+          <t>6–17–22–57–62</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
         <v>3</v>
@@ -1107,19 +1107,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>02/08/2022</t>
+          <t>02/18/2022</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1–17–20–52–54</t>
+          <t>6–11–50–63–68</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -1128,19 +1128,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>02/04/2022</t>
+          <t>02/15/2022</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>7–16–34–44–61</t>
+          <t>2–4–15–21–63</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -1149,19 +1149,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>02/01/2022</t>
+          <t>02/11/2022</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>11–24–38–62–66</t>
+          <t>11–16–23–24–30</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1170,16 +1170,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01/28/2022</t>
+          <t>02/08/2022</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3–16–25–44–55</t>
+          <t>1–17–20–52–54</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
         <v>3</v>
@@ -1191,19 +1191,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01/25/2022</t>
+          <t>02/04/2022</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3–12–38–53–58</t>
+          <t>7–16–34–44–61</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -1212,19 +1212,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01/21/2022</t>
+          <t>02/01/2022</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>38–45–46–55–67</t>
+          <t>11–24–38–62–66</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -1233,19 +1233,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01/18/2022</t>
+          <t>01/28/2022</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4–19–39–42–52</t>
+          <t>3–16–25–44–55</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -1254,19 +1254,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01/14/2022</t>
+          <t>01/25/2022</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5–8–13–22–48</t>
+          <t>3–12–38–53–58</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -1275,16 +1275,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01/11/2022</t>
+          <t>01/21/2022</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2–3–19–52–58</t>
+          <t>38–45–46–55–67</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E41" t="n">
         <v>2</v>
@@ -1296,19 +1296,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01/07/2022</t>
+          <t>01/18/2022</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>7–29–43–56–57</t>
+          <t>4–19–39–42–52</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -1317,19 +1317,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
+          <t>01/14/2022</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>4–6–16–21–22</t>
+          <t>5–8–13–22–48</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1338,19 +1338,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12/31/2021</t>
+          <t>01/11/2022</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2–5–30–46–61</t>
+          <t>2–3–19–52–58</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1359,16 +1359,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12/28/2021</t>
+          <t>01/07/2022</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>3–5–8–31–38</t>
+          <t>7–29–43–56–57</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
         <v>3</v>
@@ -1380,19 +1380,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12/24/2021</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>16–17–25–36–37</t>
+          <t>4–6–16–21–22</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1401,16 +1401,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12/21/2021</t>
+          <t>12/31/2021</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>25–31–58–64–67</t>
+          <t>2–5–30–46–61</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E47" t="n">
         <v>3</v>
@@ -1422,16 +1422,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12/17/2021</t>
+          <t>12/28/2021</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>21–32–38–48–62</t>
+          <t>3–5–8–31–38</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
         <v>3</v>
@@ -1443,19 +1443,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12/14/2021</t>
+          <t>12/24/2021</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>33–35–44–55–69</t>
+          <t>16–17–25–36–37</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -1464,19 +1464,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12/10/2021</t>
+          <t>12/21/2021</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>23–25–40–42–60</t>
+          <t>25–31–58–64–67</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -1485,19 +1485,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12/07/2021</t>
+          <t>12/17/2021</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1–7–40–43–68</t>
+          <t>21–32–38–48–62</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -1506,19 +1506,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12/03/2021</t>
+          <t>12/14/2021</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>22–45–48–58–61</t>
+          <t>33–35–44–55–69</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -1527,16 +1527,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11/30/2021</t>
+          <t>12/10/2021</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>7–8–26–30–39</t>
+          <t>23–25–40–42–60</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E53" t="n">
         <v>2</v>
@@ -1548,16 +1548,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>11/26/2021</t>
+          <t>12/07/2021</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>7–27–37–42–59</t>
+          <t>1–7–40–43–68</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
@@ -1569,19 +1569,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11/23/2021</t>
+          <t>12/03/2021</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>7–24–54–57–58</t>
+          <t>22–45–48–58–61</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -1590,19 +1590,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11/19/2021</t>
+          <t>11/30/2021</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>5–23–52–53–59</t>
+          <t>7–8–26–30–39</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -1611,19 +1611,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11/16/2021</t>
+          <t>11/26/2021</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>6–22–44–53–65</t>
+          <t>7–27–37–42–59</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -1632,19 +1632,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11/12/2021</t>
+          <t>11/23/2021</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>30–32–42–46–48</t>
+          <t>7–24–54–57–58</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1653,19 +1653,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11/09/2021</t>
+          <t>11/19/2021</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9–14–16–26–49</t>
+          <t>5–23–52–53–59</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -1674,19 +1674,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11/05/2021</t>
+          <t>11/16/2021</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>10–15–20–66–68</t>
+          <t>6–22–44–53–65</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -1695,16 +1695,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>11/02/2021</t>
+          <t>11/12/2021</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>5–10–26–58–65</t>
+          <t>30–32–42–46–48</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E61" t="n">
         <v>2</v>
@@ -1716,16 +1716,16 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>10/29/2021</t>
+          <t>11/09/2021</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>15–26–28–35–45</t>
+          <t>9–14–16–26–49</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E62" t="n">
         <v>3</v>
@@ -1737,19 +1737,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>10/26/2021</t>
+          <t>11/05/2021</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>6–14–19–56–62</t>
+          <t>10–15–20–66–68</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -1758,19 +1758,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>10/22/2021</t>
+          <t>11/02/2021</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>9–14–26–29–66</t>
+          <t>5–10–26–58–65</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -1779,16 +1779,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>10/19/2021</t>
+          <t>10/29/2021</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>3–12–13–19–52</t>
+          <t>15–26–28–35–45</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E65" t="n">
         <v>3</v>
@@ -1800,19 +1800,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10/15/2021</t>
+          <t>10/26/2021</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>3–20–31–34–65</t>
+          <t>6–14–19–56–62</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -1821,16 +1821,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>10/12/2021</t>
+          <t>10/22/2021</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>21–26–56–61–65</t>
+          <t>9–14–26–29–66</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E67" t="n">
         <v>3</v>
@@ -1842,19 +1842,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>10/08/2021</t>
+          <t>10/19/2021</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>21–24–36–40–70</t>
+          <t>3–12–13–19–52</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -1863,16 +1863,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>10/05/2021</t>
+          <t>10/15/2021</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>7–11–18–30–36</t>
+          <t>3–20–31–34–65</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E69" t="n">
         <v>3</v>
@@ -1884,19 +1884,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>10/01/2021</t>
+          <t>10/12/2021</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>21–25–36–62–63</t>
+          <t>21–26–56–61–65</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -1905,19 +1905,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>09/28/2021</t>
+          <t>10/08/2021</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>18–30–43–68–69</t>
+          <t>21–24–36–40–70</t>
         </is>
       </c>
       <c r="D71" t="n">
         <v>22</v>
       </c>
       <c r="E71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -1926,16 +1926,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>09/24/2021</t>
+          <t>10/05/2021</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>17–21–27–43–56</t>
+          <t>7–11–18–30–36</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E72" t="n">
         <v>3</v>
@@ -1947,19 +1947,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>09/21/2021</t>
+          <t>10/01/2021</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>36–41–45–51–56</t>
+          <t>21–25–36–62–63</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -1968,19 +1968,19 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>09/17/2021</t>
+          <t>09/28/2021</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>17–32–40–59–61</t>
+          <t>18–30–43–68–69</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -1989,19 +1989,19 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>09/14/2021</t>
+          <t>09/24/2021</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>4–13–19–63–64</t>
+          <t>17–21–27–43–56</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -2010,19 +2010,19 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>09/10/2021</t>
+          <t>09/21/2021</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>20–32–35–47–64</t>
+          <t>36–41–45–51–56</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -2031,16 +2031,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>09/07/2021</t>
+          <t>09/17/2021</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>15–17–25–32–53</t>
+          <t>17–32–40–59–61</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E77" t="n">
         <v>3</v>
@@ -2052,16 +2052,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>09/03/2021</t>
+          <t>09/14/2021</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>7–10–12–61–65</t>
+          <t>4–13–19–63–64</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E78" t="n">
         <v>2</v>
@@ -2073,19 +2073,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>08/31/2021</t>
+          <t>09/10/2021</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>8–14–31–58–68</t>
+          <t>20–32–35–47–64</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2094,16 +2094,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>08/27/2021</t>
+          <t>09/07/2021</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1–10–44–47–56</t>
+          <t>15–17–25–32–53</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E80" t="n">
         <v>3</v>
@@ -2115,16 +2115,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>08/24/2021</t>
+          <t>09/03/2021</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>17–18–26–52–67</t>
+          <t>7–10–12–61–65</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
         <v>2</v>
@@ -2136,19 +2136,19 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>08/20/2021</t>
+          <t>08/31/2021</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>41–43–51–57–70</t>
+          <t>8–14–31–58–68</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2157,16 +2157,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>08/17/2021</t>
+          <t>08/27/2021</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>3–6–16–38–56</t>
+          <t>1–10–44–47–56</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E83" t="n">
         <v>3</v>
@@ -2178,16 +2178,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>08/13/2021</t>
+          <t>08/24/2021</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>17–21–35–40–53</t>
+          <t>17–18–26–52–67</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
@@ -2199,16 +2199,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>08/10/2021</t>
+          <t>08/20/2021</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>29–45–50–59–62</t>
+          <t>41–43–51–57–70</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
         <v>2</v>
@@ -2220,19 +2220,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>08/06/2021</t>
+          <t>08/17/2021</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>9–18–40–46–69</t>
+          <t>3–6–16–38–56</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -2241,16 +2241,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>08/03/2021</t>
+          <t>08/13/2021</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1–9–17–27–34</t>
+          <t>17–21–35–40–53</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E87" t="n">
         <v>2</v>
@@ -2262,19 +2262,19 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>07/30/2021</t>
+          <t>08/10/2021</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>19–26–31–52–68</t>
+          <t>29–45–50–59–62</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -2283,19 +2283,19 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>07/27/2021</t>
+          <t>08/06/2021</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2–35–36–54–64</t>
+          <t>9–18–40–46–69</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -2304,19 +2304,19 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>07/23/2021</t>
+          <t>08/03/2021</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>13–17–19–40–69</t>
+          <t>1–9–17–27–34</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -2325,19 +2325,19 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>07/20/2021</t>
+          <t>07/30/2021</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>10–26–30–52–57</t>
+          <t>19–26–31–52–68</t>
         </is>
       </c>
       <c r="D91" t="n">
         <v>10</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
@@ -2346,19 +2346,19 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>07/16/2021</t>
+          <t>07/27/2021</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>24–25–47–52–57</t>
+          <t>2–35–36–54–64</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -2367,19 +2367,19 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>07/13/2021</t>
+          <t>07/23/2021</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>3–10–17–26–55</t>
+          <t>13–17–19–40–69</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -2388,16 +2388,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>07/09/2021</t>
+          <t>07/20/2021</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>6–37–39–41–46</t>
+          <t>10–26–30–52–57</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E94" t="n">
         <v>2</v>
@@ -2409,19 +2409,19 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>07/06/2021</t>
+          <t>07/16/2021</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>18–47–63–68–69</t>
+          <t>24–25–47–52–57</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
@@ -2430,16 +2430,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>07/02/2021</t>
+          <t>07/13/2021</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>8–31–32–34–45</t>
+          <t>3–10–17–26–55</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E96" t="n">
         <v>2</v>
@@ -2451,19 +2451,19 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>06/29/2021</t>
+          <t>07/09/2021</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>7–38–50–52–69</t>
+          <t>6–37–39–41–46</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -2472,19 +2472,19 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>06/25/2021</t>
+          <t>07/06/2021</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>17–20–42–45–65</t>
+          <t>18–47–63–68–69</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -2493,19 +2493,19 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>06/22/2021</t>
+          <t>07/02/2021</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1–26–48–51–59</t>
+          <t>8–31–32–34–45</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -2514,19 +2514,19 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>06/18/2021</t>
+          <t>06/29/2021</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>14–36–44–46–53</t>
+          <t>7–38–50–52–69</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -2535,16 +2535,16 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>06/15/2021</t>
+          <t>06/25/2021</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>18–22–27–38–52</t>
+          <t>17–20–42–45–65</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E101" t="n">
         <v>4</v>
@@ -2556,16 +2556,16 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>06/11/2021</t>
+          <t>06/22/2021</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>4–43–56–63–68</t>
+          <t>1–26–48–51–59</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E102" t="n">
         <v>4</v>
@@ -2577,19 +2577,19 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>06/08/2021</t>
+          <t>06/18/2021</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>9–22–39–41–54</t>
+          <t>14–36–44–46–53</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2598,19 +2598,19 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>06/04/2021</t>
+          <t>06/15/2021</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4–30–34–41–64</t>
+          <t>18–22–27–38–52</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
@@ -2619,19 +2619,19 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>06/01/2021</t>
+          <t>06/11/2021</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>7–11–33–58–63</t>
+          <t>4–43–56–63–68</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106">
@@ -2640,19 +2640,19 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>05/28/2021</t>
+          <t>06/08/2021</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>10–14–20–47–70</t>
+          <t>9–22–39–41–54</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/lottopy_site/lottopy/lottopy_web_edition/lotto_megamil.xlsx
+++ b/lottopy_site/lottopy/lottopy_web_edition/lotto_megamil.xlsx
@@ -456,19 +456,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06/07/2022</t>
+          <t>06/10/2022</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4–34–40–41–53</t>
+          <t>3–12–14–18–32</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06/03/2022</t>
+          <t>06/07/2022</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11–16–22–48–59</t>
+          <t>4–34–40–41–53</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>4</v>
@@ -498,16 +498,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05/31/2022</t>
+          <t>06/03/2022</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6–15–41–63–64</t>
+          <t>11–16–22–48–59</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
@@ -519,19 +519,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05/27/2022</t>
+          <t>05/31/2022</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3–14–40–53–54</t>
+          <t>6–15–41–63–64</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -540,16 +540,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05/24/2022</t>
+          <t>05/27/2022</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3–5–6–63–68</t>
+          <t>3–14–40–53–54</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -561,16 +561,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05/20/2022</t>
+          <t>05/24/2022</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>33–40–59–60–69</t>
+          <t>3–5–6–63–68</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -582,19 +582,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>05/17/2022</t>
+          <t>05/20/2022</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7–21–24–41–65</t>
+          <t>33–40–59–60–69</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -603,19 +603,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>05/13/2022</t>
+          <t>05/17/2022</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11–41–43–44–65</t>
+          <t>7–21–24–41–65</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -624,16 +624,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>05/10/2022</t>
+          <t>05/13/2022</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15–19–20–61–70</t>
+          <t>11–41–43–44–65</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -645,19 +645,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>05/06/2022</t>
+          <t>05/10/2022</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16–21–33–52–70</t>
+          <t>15–19–20–61–70</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -666,16 +666,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>05/03/2022</t>
+          <t>05/06/2022</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15–19–27–35–57</t>
+          <t>16–21–33–52–70</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -687,16 +687,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>04/29/2022</t>
+          <t>05/03/2022</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9–11–34–49–66</t>
+          <t>15–19–27–35–57</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
@@ -708,19 +708,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>04/26/2022</t>
+          <t>04/29/2022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5–7–19–46–69</t>
+          <t>9–11–34–49–66</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -729,19 +729,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>04/22/2022</t>
+          <t>04/26/2022</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7–28–29–58–59</t>
+          <t>5–7–19–46–69</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -750,16 +750,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>04/19/2022</t>
+          <t>04/22/2022</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2–9–33–47–53</t>
+          <t>7–28–29–58–59</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
@@ -771,19 +771,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>04/15/2022</t>
+          <t>04/19/2022</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4–17–20–46–64</t>
+          <t>2–9–33–47–53</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -792,19 +792,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>04/12/2022</t>
+          <t>04/15/2022</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2–8–14–20–31</t>
+          <t>4–17–20–46–64</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -813,19 +813,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>04/08/2022</t>
+          <t>04/12/2022</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>8–11–29–32–40</t>
+          <t>2–8–14–20–31</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -834,19 +834,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>04/05/2022</t>
+          <t>04/08/2022</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>22–43–60–63–64</t>
+          <t>8–11–29–32–40</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -855,19 +855,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>04/01/2022</t>
+          <t>04/05/2022</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>26–42–47–48–63</t>
+          <t>22–43–60–63–64</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -876,19 +876,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>03/29/2022</t>
+          <t>04/01/2022</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7–22–36–45–47</t>
+          <t>26–42–47–48–63</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -897,16 +897,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>03/25/2022</t>
+          <t>03/29/2022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3–13–42–51–58</t>
+          <t>7–22–36–45–47</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -918,19 +918,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>03/22/2022</t>
+          <t>03/25/2022</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>8–15–21–27–61</t>
+          <t>3–13–42–51–58</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -939,19 +939,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>03/18/2022</t>
+          <t>03/22/2022</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2–6–25–40–45</t>
+          <t>8–15–21–27–61</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -960,19 +960,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>03/15/2022</t>
+          <t>03/18/2022</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9–14–28–59–60</t>
+          <t>2–6–25–40–45</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -981,19 +981,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>03/11/2022</t>
+          <t>03/15/2022</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>24–28–39–44–66</t>
+          <t>9–14–28–59–60</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -1002,16 +1002,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>03/08/2022</t>
+          <t>03/11/2022</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7–18–38–58–64</t>
+          <t>24–28–39–44–66</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E28" t="n">
         <v>3</v>
@@ -1023,19 +1023,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>03/04/2022</t>
+          <t>03/08/2022</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>11–19–28–46–47</t>
+          <t>7–18–38–58–64</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1044,19 +1044,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>03/01/2022</t>
+          <t>03/04/2022</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18–22–38–39–50</t>
+          <t>11–19–28–46–47</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1065,19 +1065,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>02/25/2022</t>
+          <t>03/01/2022</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>15–31–40–56–66</t>
+          <t>18–22–38–39–50</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1086,16 +1086,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>02/22/2022</t>
+          <t>02/25/2022</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>6–17–22–57–62</t>
+          <t>15–31–40–56–66</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
         <v>3</v>
@@ -1107,19 +1107,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>02/18/2022</t>
+          <t>02/22/2022</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6–11–50–63–68</t>
+          <t>6–17–22–57–62</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1128,19 +1128,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>02/15/2022</t>
+          <t>02/18/2022</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2–4–15–21–63</t>
+          <t>6–11–50–63–68</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -1149,16 +1149,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>02/11/2022</t>
+          <t>02/15/2022</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>11–16–23–24–30</t>
+          <t>2–4–15–21–63</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E35" t="n">
         <v>3</v>
@@ -1170,16 +1170,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>02/08/2022</t>
+          <t>02/11/2022</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1–17–20–52–54</t>
+          <t>11–16–23–24–30</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E36" t="n">
         <v>3</v>
@@ -1191,19 +1191,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>02/04/2022</t>
+          <t>02/08/2022</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>7–16–34–44–61</t>
+          <t>1–17–20–52–54</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1212,16 +1212,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>02/01/2022</t>
+          <t>02/04/2022</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>11–24–38–62–66</t>
+          <t>7–16–34–44–61</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E38" t="n">
         <v>4</v>
@@ -1233,19 +1233,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01/28/2022</t>
+          <t>02/01/2022</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>3–16–25–44–55</t>
+          <t>11–24–38–62–66</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01/25/2022</t>
+          <t>01/28/2022</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3–12–38–53–58</t>
+          <t>3–16–25–44–55</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1275,19 +1275,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01/21/2022</t>
+          <t>01/25/2022</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>38–45–46–55–67</t>
+          <t>3–12–38–53–58</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1296,19 +1296,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01/18/2022</t>
+          <t>01/21/2022</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4–19–39–42–52</t>
+          <t>38–45–46–55–67</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1317,19 +1317,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01/14/2022</t>
+          <t>01/18/2022</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5–8–13–22–48</t>
+          <t>4–19–39–42–52</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -1338,16 +1338,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01/11/2022</t>
+          <t>01/14/2022</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2–3–19–52–58</t>
+          <t>5–8–13–22–48</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E44" t="n">
         <v>2</v>
@@ -1359,19 +1359,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01/07/2022</t>
+          <t>01/11/2022</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>7–29–43–56–57</t>
+          <t>2–3–19–52–58</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1380,16 +1380,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
+          <t>01/07/2022</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4–6–16–21–22</t>
+          <t>7–29–43–56–57</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E46" t="n">
         <v>3</v>
@@ -1401,16 +1401,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12/31/2021</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2–5–30–46–61</t>
+          <t>4–6–16–21–22</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>3</v>
@@ -1422,16 +1422,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12/28/2021</t>
+          <t>12/31/2021</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3–5–8–31–38</t>
+          <t>2–5–30–46–61</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E48" t="n">
         <v>3</v>
@@ -1443,19 +1443,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12/24/2021</t>
+          <t>12/28/2021</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>16–17–25–36–37</t>
+          <t>3–5–8–31–38</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -1464,19 +1464,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12/21/2021</t>
+          <t>12/24/2021</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>25–31–58–64–67</t>
+          <t>16–17–25–36–37</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12/17/2021</t>
+          <t>12/21/2021</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>21–32–38–48–62</t>
+          <t>25–31–58–64–67</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E51" t="n">
         <v>3</v>
@@ -1506,16 +1506,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12/14/2021</t>
+          <t>12/17/2021</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>33–35–44–55–69</t>
+          <t>21–32–38–48–62</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E52" t="n">
         <v>3</v>
@@ -1527,19 +1527,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12/10/2021</t>
+          <t>12/14/2021</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>23–25–40–42–60</t>
+          <t>33–35–44–55–69</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -1548,16 +1548,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12/07/2021</t>
+          <t>12/10/2021</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1–7–40–43–68</t>
+          <t>23–25–40–42–60</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
@@ -1569,19 +1569,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12/03/2021</t>
+          <t>12/07/2021</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>22–45–48–58–61</t>
+          <t>1–7–40–43–68</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -1590,19 +1590,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11/30/2021</t>
+          <t>12/03/2021</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>7–8–26–30–39</t>
+          <t>22–45–48–58–61</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -1611,16 +1611,16 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11/26/2021</t>
+          <t>11/30/2021</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>7–27–37–42–59</t>
+          <t>7–8–26–30–39</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E57" t="n">
         <v>2</v>
@@ -1632,19 +1632,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11/23/2021</t>
+          <t>11/26/2021</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>7–24–54–57–58</t>
+          <t>7–27–37–42–59</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -1653,19 +1653,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11/19/2021</t>
+          <t>11/23/2021</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>5–23–52–53–59</t>
+          <t>7–24–54–57–58</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -1674,19 +1674,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11/16/2021</t>
+          <t>11/19/2021</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>6–22–44–53–65</t>
+          <t>5–23–52–53–59</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -1695,19 +1695,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>11/12/2021</t>
+          <t>11/16/2021</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>30–32–42–46–48</t>
+          <t>6–22–44–53–65</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -1716,19 +1716,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>11/09/2021</t>
+          <t>11/12/2021</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9–14–16–26–49</t>
+          <t>30–32–42–46–48</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -1737,19 +1737,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11/05/2021</t>
+          <t>11/09/2021</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>10–15–20–66–68</t>
+          <t>9–14–16–26–49</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -1758,16 +1758,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11/02/2021</t>
+          <t>11/05/2021</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>5–10–26–58–65</t>
+          <t>10–15–20–66–68</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E64" t="n">
         <v>2</v>
@@ -1779,19 +1779,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>10/29/2021</t>
+          <t>11/02/2021</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>15–26–28–35–45</t>
+          <t>5–10–26–58–65</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -1800,19 +1800,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10/26/2021</t>
+          <t>10/29/2021</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>6–14–19–56–62</t>
+          <t>15–26–28–35–45</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -1821,19 +1821,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>10/22/2021</t>
+          <t>10/26/2021</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>9–14–26–29–66</t>
+          <t>6–14–19–56–62</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -1842,16 +1842,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>10/19/2021</t>
+          <t>10/22/2021</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>3–12–13–19–52</t>
+          <t>9–14–26–29–66</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E68" t="n">
         <v>3</v>
@@ -1863,16 +1863,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>10/15/2021</t>
+          <t>10/19/2021</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>3–20–31–34–65</t>
+          <t>3–12–13–19–52</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
         <v>3</v>
@@ -1884,16 +1884,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>10/12/2021</t>
+          <t>10/15/2021</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>21–26–56–61–65</t>
+          <t>3–20–31–34–65</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E70" t="n">
         <v>3</v>
@@ -1905,19 +1905,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>10/08/2021</t>
+          <t>10/12/2021</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>21–24–36–40–70</t>
+          <t>21–26–56–61–65</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -1926,19 +1926,19 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>10/05/2021</t>
+          <t>10/08/2021</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>7–11–18–30–36</t>
+          <t>21–24–36–40–70</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -1947,19 +1947,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>10/01/2021</t>
+          <t>10/05/2021</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>21–25–36–62–63</t>
+          <t>7–11–18–30–36</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -1968,19 +1968,19 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>09/28/2021</t>
+          <t>10/01/2021</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>18–30–43–68–69</t>
+          <t>21–25–36–62–63</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -1989,19 +1989,19 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>09/24/2021</t>
+          <t>09/28/2021</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>17–21–27–43–56</t>
+          <t>18–30–43–68–69</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -2010,16 +2010,16 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>09/21/2021</t>
+          <t>09/24/2021</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>36–41–45–51–56</t>
+          <t>17–21–27–43–56</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E76" t="n">
         <v>3</v>
@@ -2031,16 +2031,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>09/17/2021</t>
+          <t>09/21/2021</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>17–32–40–59–61</t>
+          <t>36–41–45–51–56</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E77" t="n">
         <v>3</v>
@@ -2052,19 +2052,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>09/14/2021</t>
+          <t>09/17/2021</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>4–13–19–63–64</t>
+          <t>17–32–40–59–61</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2073,16 +2073,16 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>09/10/2021</t>
+          <t>09/14/2021</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>20–32–35–47–64</t>
+          <t>4–13–19–63–64</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E79" t="n">
         <v>2</v>
@@ -2094,19 +2094,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>09/07/2021</t>
+          <t>09/10/2021</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>15–17–25–32–53</t>
+          <t>20–32–35–47–64</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2115,19 +2115,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>09/03/2021</t>
+          <t>09/07/2021</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>7–10–12–61–65</t>
+          <t>15–17–25–32–53</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -2136,19 +2136,19 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>08/31/2021</t>
+          <t>09/03/2021</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>8–14–31–58–68</t>
+          <t>7–10–12–61–65</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2157,16 +2157,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>08/27/2021</t>
+          <t>08/31/2021</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>1–10–44–47–56</t>
+          <t>8–14–31–58–68</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E83" t="n">
         <v>3</v>
@@ -2178,19 +2178,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>08/24/2021</t>
+          <t>08/27/2021</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>17–18–26–52–67</t>
+          <t>1–10–44–47–56</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2199,16 +2199,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>08/20/2021</t>
+          <t>08/24/2021</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>41–43–51–57–70</t>
+          <t>17–18–26–52–67</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E85" t="n">
         <v>2</v>
@@ -2220,19 +2220,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>08/17/2021</t>
+          <t>08/20/2021</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>3–6–16–38–56</t>
+          <t>41–43–51–57–70</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2241,19 +2241,19 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>08/13/2021</t>
+          <t>08/17/2021</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>17–21–35–40–53</t>
+          <t>3–6–16–38–56</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
@@ -2262,16 +2262,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>08/10/2021</t>
+          <t>08/13/2021</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>29–45–50–59–62</t>
+          <t>17–21–35–40–53</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E88" t="n">
         <v>2</v>
@@ -2283,16 +2283,16 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>08/06/2021</t>
+          <t>08/10/2021</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>9–18–40–46–69</t>
+          <t>29–45–50–59–62</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E89" t="n">
         <v>2</v>
@@ -2304,16 +2304,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>08/03/2021</t>
+          <t>08/06/2021</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1–9–17–27–34</t>
+          <t>9–18–40–46–69</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E90" t="n">
         <v>2</v>
@@ -2325,19 +2325,19 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>07/30/2021</t>
+          <t>08/03/2021</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>19–26–31–52–68</t>
+          <t>1–9–17–27–34</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -2346,16 +2346,16 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>07/27/2021</t>
+          <t>07/30/2021</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2–35–36–54–64</t>
+          <t>19–26–31–52–68</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E92" t="n">
         <v>3</v>
@@ -2367,16 +2367,16 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>07/23/2021</t>
+          <t>07/27/2021</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>13–17–19–40–69</t>
+          <t>2–35–36–54–64</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E93" t="n">
         <v>3</v>
@@ -2388,19 +2388,19 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>07/20/2021</t>
+          <t>07/23/2021</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>10–26–30–52–57</t>
+          <t>13–17–19–40–69</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
@@ -2409,19 +2409,19 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>07/16/2021</t>
+          <t>07/20/2021</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>24–25–47–52–57</t>
+          <t>10–26–30–52–57</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -2430,19 +2430,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>07/13/2021</t>
+          <t>07/16/2021</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>3–10–17–26–55</t>
+          <t>24–25–47–52–57</t>
         </is>
       </c>
       <c r="D96" t="n">
         <v>24</v>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
@@ -2451,16 +2451,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>07/09/2021</t>
+          <t>07/13/2021</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>6–37–39–41–46</t>
+          <t>3–10–17–26–55</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E97" t="n">
         <v>2</v>
@@ -2472,19 +2472,19 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>07/06/2021</t>
+          <t>07/09/2021</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>18–47–63–68–69</t>
+          <t>6–37–39–41–46</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -2493,19 +2493,19 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>07/02/2021</t>
+          <t>07/06/2021</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>8–31–32–34–45</t>
+          <t>18–47–63–68–69</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -2514,19 +2514,19 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>06/29/2021</t>
+          <t>07/02/2021</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>7–38–50–52–69</t>
+          <t>8–31–32–34–45</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -2535,19 +2535,19 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>06/25/2021</t>
+          <t>06/29/2021</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>17–20–42–45–65</t>
+          <t>7–38–50–52–69</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -2556,16 +2556,16 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>06/22/2021</t>
+          <t>06/25/2021</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1–26–48–51–59</t>
+          <t>17–20–42–45–65</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E102" t="n">
         <v>4</v>
@@ -2577,19 +2577,19 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>06/18/2021</t>
+          <t>06/22/2021</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>14–36–44–46–53</t>
+          <t>1–26–48–51–59</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E103" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
@@ -2598,19 +2598,19 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>06/15/2021</t>
+          <t>06/18/2021</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>18–22–27–38–52</t>
+          <t>14–36–44–46–53</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E104" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -2619,16 +2619,16 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>06/11/2021</t>
+          <t>06/15/2021</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4–43–56–63–68</t>
+          <t>18–22–27–38–52</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E105" t="n">
         <v>4</v>
@@ -2640,19 +2640,19 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>06/08/2021</t>
+          <t>06/11/2021</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>9–22–39–41–54</t>
+          <t>4–43–56–63–68</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
